--- a/MVP_Effort_Estimation_Aurion.xlsx
+++ b/MVP_Effort_Estimation_Aurion.xlsx
@@ -2311,7 +2311,7 @@
       </c>
       <c r="K14" s="37" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L14" s="37" t="inlineStr">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="L7" s="37" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="M7" s="37" t="inlineStr">
@@ -5862,7 +5862,7 @@
       </c>
       <c r="L28" s="37" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="M28" s="37" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="L29" s="37" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="M29" s="37" t="inlineStr">
@@ -6044,7 +6044,7 @@
       </c>
       <c r="L30" s="37" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="M30" s="37" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="L31" s="37" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="M31" s="37" t="inlineStr">
@@ -8241,7 +8241,7 @@
       </c>
       <c r="M21" s="37" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="N21" s="37" t="inlineStr">
